--- a/Parallax_Portfolio_of_the_Week_2026-06-15.xlsx
+++ b/Parallax_Portfolio_of_the_Week_2026-06-15.xlsx
@@ -436,7 +436,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -451,7 +451,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -466,7 +466,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -481,7 +481,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -496,7 +496,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -511,7 +511,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -526,12 +526,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -541,12 +541,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>MRVL</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -556,12 +556,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -571,12 +571,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -586,12 +586,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -601,12 +601,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -616,12 +616,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -631,12 +631,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MRVL</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -646,12 +646,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>NEM</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -661,12 +661,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ELV</t>
+          <t>GOLD</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -676,12 +676,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>HUM</t>
+          <t>AEM</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -691,12 +691,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>KGC</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -706,12 +706,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CVS</t>
+          <t>WPM</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -721,12 +721,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>FNV</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -736,12 +736,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NOC</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -751,12 +751,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -766,12 +766,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -781,12 +781,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -796,12 +796,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -811,12 +811,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -826,12 +826,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -841,12 +841,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>DUK</t>
+          <t>WMT</t>
         </is>
       </c>
       <c r="C29" t="n">
